--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_valparaiso.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_valparaiso.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>25.47089952585468</v>
+      </c>
+      <c r="C2">
         <v>36.60526493453887</v>
-      </c>
-      <c r="C2">
-        <v>25.47089952585468</v>
       </c>
       <c r="D2">
         <v>2.731847459069886</v>
       </c>
       <c r="E2">
-        <v>22.58522408671885</v>
+        <v>15.71538887945426</v>
       </c>
       <c r="F2">
         <v>61.69938703382689</v>
       </c>
       <c r="G2">
-        <v>15.71538887945426</v>
+        <v>22.58522408671885</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.38493828394383</v>
+      </c>
+      <c r="C3">
         <v>32.02238768677228</v>
-      </c>
-      <c r="C3">
-        <v>27.38493828394383</v>
       </c>
       <c r="D3">
         <v>3.122815230961298</v>
       </c>
       <c r="E3">
-        <v>20.08840402520455</v>
+        <v>17.17922191918242</v>
       </c>
       <c r="F3">
         <v>62.73237405561303</v>
       </c>
       <c r="G3">
-        <v>17.17922191918242</v>
+        <v>20.08840402520455</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.50244309379097</v>
+      </c>
+      <c r="C4">
         <v>32.46037421046359</v>
-      </c>
-      <c r="C4">
-        <v>24.50244309379097</v>
       </c>
       <c r="D4">
         <v>3.080679210647086</v>
       </c>
       <c r="E4">
-        <v>20.68029535144164</v>
+        <v>15.61034868933053</v>
       </c>
       <c r="F4">
         <v>63.70935595922784</v>
       </c>
       <c r="G4">
-        <v>15.61034868933053</v>
+        <v>20.68029535144164</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>36.45038167938932</v>
+      </c>
+      <c r="C5">
         <v>32.06106870229008</v>
-      </c>
-      <c r="C5">
-        <v>36.45038167938932</v>
       </c>
       <c r="D5">
         <v>3.119047619047619</v>
       </c>
       <c r="E5">
-        <v>19.02604756511892</v>
+        <v>21.63080407701019</v>
       </c>
       <c r="F5">
         <v>59.34314835787089</v>
       </c>
       <c r="G5">
-        <v>21.63080407701019</v>
+        <v>19.02604756511892</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.52280701754386</v>
+      </c>
+      <c r="C6">
         <v>39.1859649122807</v>
-      </c>
-      <c r="C6">
-        <v>29.52280701754386</v>
       </c>
       <c r="D6">
         <v>2.551934097421203</v>
       </c>
       <c r="E6">
-        <v>23.2269872301485</v>
+        <v>17.49927207686868</v>
       </c>
       <c r="F6">
         <v>59.27374069298282</v>
       </c>
       <c r="G6">
-        <v>17.49927207686868</v>
+        <v>23.2269872301485</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>31.07475552671826</v>
+      </c>
+      <c r="C7">
         <v>36.53427260508875</v>
-      </c>
-      <c r="C7">
-        <v>31.07475552671826</v>
       </c>
       <c r="D7">
         <v>2.737155905112267</v>
       </c>
       <c r="E7">
-        <v>21.79731784874879</v>
+        <v>18.54002488593945</v>
       </c>
       <c r="F7">
         <v>59.66265726531177</v>
       </c>
       <c r="G7">
-        <v>18.54002488593945</v>
+        <v>21.79731784874879</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>24.58907741251326</v>
+      </c>
+      <c r="C8">
         <v>39.22322375397667</v>
-      </c>
-      <c r="C8">
-        <v>24.58907741251326</v>
       </c>
       <c r="D8">
         <v>2.549509969584319</v>
       </c>
       <c r="E8">
-        <v>23.94400388412364</v>
+        <v>15.01051950153747</v>
       </c>
       <c r="F8">
         <v>61.04547661433889</v>
       </c>
       <c r="G8">
-        <v>15.01051950153747</v>
+        <v>23.94400388412364</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.68578993821712</v>
+      </c>
+      <c r="C9">
         <v>18.44660194174757</v>
-      </c>
-      <c r="C9">
-        <v>31.68578993821712</v>
       </c>
       <c r="D9">
         <v>5.421052631578948</v>
       </c>
       <c r="E9">
-        <v>12.28689006466784</v>
+        <v>21.10523221634332</v>
       </c>
       <c r="F9">
         <v>66.60787771898883</v>
       </c>
       <c r="G9">
-        <v>21.10523221634332</v>
+        <v>12.28689006466784</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.46127051058759</v>
+      </c>
+      <c r="C10">
         <v>33.97653313777615</v>
-      </c>
-      <c r="C10">
-        <v>27.46127051058759</v>
       </c>
       <c r="D10">
         <v>2.943207878052071</v>
       </c>
       <c r="E10">
-        <v>21.046206260203</v>
+        <v>17.01043367165874</v>
       </c>
       <c r="F10">
         <v>61.94336006813826</v>
       </c>
       <c r="G10">
-        <v>17.01043367165874</v>
+        <v>21.046206260203</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.76675738332829</v>
+      </c>
+      <c r="C11">
         <v>28.76726136478178</v>
-      </c>
-      <c r="C11">
-        <v>33.76675738332829</v>
       </c>
       <c r="D11">
         <v>3.476173791170287</v>
       </c>
       <c r="E11">
-        <v>17.69922480620155</v>
+        <v>20.77519379844961</v>
       </c>
       <c r="F11">
         <v>61.52558139534884</v>
       </c>
       <c r="G11">
-        <v>20.77519379844961</v>
+        <v>17.69922480620155</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>32.39026969857218</v>
+      </c>
+      <c r="C12">
         <v>30.01057641459545</v>
-      </c>
-      <c r="C12">
-        <v>32.39026969857218</v>
       </c>
       <c r="D12">
         <v>3.33215859030837</v>
       </c>
       <c r="E12">
-        <v>18.47932269619017</v>
+        <v>19.94464343861934</v>
       </c>
       <c r="F12">
         <v>61.5760338651905</v>
       </c>
       <c r="G12">
-        <v>19.94464343861934</v>
+        <v>18.47932269619017</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>29.32980462364754</v>
+      </c>
+      <c r="C13">
         <v>32.2643418696972</v>
-      </c>
-      <c r="C13">
-        <v>29.32980462364754</v>
       </c>
       <c r="D13">
         <v>3.099396863691194</v>
       </c>
       <c r="E13">
-        <v>19.96628131021195</v>
+        <v>18.15028901734104</v>
       </c>
       <c r="F13">
         <v>61.88342967244701</v>
       </c>
       <c r="G13">
-        <v>18.15028901734104</v>
+        <v>19.96628131021195</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>28.27925270403146</v>
+      </c>
+      <c r="C14">
         <v>36.29498525073746</v>
-      </c>
-      <c r="C14">
-        <v>28.27925270403146</v>
       </c>
       <c r="D14">
         <v>2.75520156046814</v>
       </c>
       <c r="E14">
-        <v>22.05386803049495</v>
+        <v>17.18328035752695</v>
       </c>
       <c r="F14">
         <v>60.76285161197811</v>
       </c>
       <c r="G14">
-        <v>17.18328035752695</v>
+        <v>22.05386803049495</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.63631132211193</v>
+      </c>
+      <c r="C15">
         <v>33.84405121565242</v>
-      </c>
-      <c r="C15">
-        <v>27.63631132211193</v>
       </c>
       <c r="D15">
         <v>2.954729011689692</v>
       </c>
       <c r="E15">
+        <v>17.11434807786538</v>
+      </c>
+      <c r="F15">
+        <v>61.92703461178672</v>
+      </c>
+      <c r="G15">
         <v>20.9586173103479</v>
-      </c>
-      <c r="F15">
-        <v>61.92703461178671</v>
-      </c>
-      <c r="G15">
-        <v>17.11434807786538</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.96074154852781</v>
+      </c>
+      <c r="C16">
         <v>38.77862595419847</v>
-      </c>
-      <c r="C16">
-        <v>27.96074154852781</v>
       </c>
       <c r="D16">
         <v>2.578740157480315</v>
       </c>
       <c r="E16">
-        <v>23.25703073904513</v>
+        <v>16.76913015042511</v>
       </c>
       <c r="F16">
         <v>59.97383911052976</v>
       </c>
       <c r="G16">
-        <v>16.76913015042511</v>
+        <v>23.25703073904513</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.74088133355339</v>
+      </c>
+      <c r="C17">
         <v>40.81531605875557</v>
-      </c>
-      <c r="C17">
-        <v>29.74088133355339</v>
       </c>
       <c r="D17">
         <v>2.450060655074808</v>
       </c>
       <c r="E17">
-        <v>23.93071414747435</v>
+        <v>17.43758467195665</v>
       </c>
       <c r="F17">
         <v>58.63170118056899</v>
       </c>
       <c r="G17">
-        <v>17.43758467195665</v>
+        <v>23.93071414747435</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>27.51572327044025</v>
+      </c>
+      <c r="C18">
         <v>40.20440251572327</v>
-      </c>
-      <c r="C18">
-        <v>27.51572327044025</v>
       </c>
       <c r="D18">
         <v>2.487289792725851</v>
       </c>
       <c r="E18">
-        <v>23.97112590231555</v>
+        <v>16.40573732070873</v>
       </c>
       <c r="F18">
         <v>59.62313677697572</v>
       </c>
       <c r="G18">
-        <v>16.40573732070873</v>
+        <v>23.97112590231555</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.34461079784821</v>
+      </c>
+      <c r="C19">
         <v>35.03953593881651</v>
-      </c>
-      <c r="C19">
-        <v>27.34461079784821</v>
       </c>
       <c r="D19">
         <v>2.853919075144509</v>
       </c>
       <c r="E19">
+        <v>16.83945837532555</v>
+      </c>
+      <c r="F19">
+        <v>61.58236626520451</v>
+      </c>
+      <c r="G19">
         <v>21.57817535946995</v>
-      </c>
-      <c r="F19">
-        <v>61.5823662652045</v>
-      </c>
-      <c r="G19">
-        <v>16.83945837532554</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>30.4862361718549</v>
+      </c>
+      <c r="C20">
         <v>26.25160792384873</v>
-      </c>
-      <c r="C20">
-        <v>30.4862361718549</v>
       </c>
       <c r="D20">
         <v>3.809290474323795</v>
       </c>
       <c r="E20">
-        <v>16.74873613026065</v>
+        <v>19.45046287177467</v>
       </c>
       <c r="F20">
         <v>63.80080099796468</v>
       </c>
       <c r="G20">
-        <v>19.45046287177467</v>
+        <v>16.74873613026065</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.7275030768117</v>
+      </c>
+      <c r="C21">
         <v>31.53551002678636</v>
-      </c>
-      <c r="C21">
-        <v>27.7275030768117</v>
       </c>
       <c r="D21">
         <v>3.171028466483012</v>
       </c>
       <c r="E21">
-        <v>19.80090004091095</v>
+        <v>17.40988226737579</v>
       </c>
       <c r="F21">
         <v>62.78921769171325</v>
       </c>
       <c r="G21">
-        <v>17.40988226737579</v>
+        <v>19.80090004091095</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.36689622417478</v>
+      </c>
+      <c r="C22">
         <v>28.37805746853479</v>
-      </c>
-      <c r="C22">
-        <v>30.36689622417478</v>
       </c>
       <c r="D22">
         <v>3.523849372384937</v>
       </c>
       <c r="E22">
-        <v>17.87650996671528</v>
+        <v>19.12936160664198</v>
       </c>
       <c r="F22">
         <v>62.99412842664273</v>
       </c>
       <c r="G22">
-        <v>19.12936160664198</v>
+        <v>17.87650996671528</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.35361684671134</v>
+      </c>
+      <c r="C23">
         <v>37.61794065363052</v>
-      </c>
-      <c r="C23">
-        <v>28.35361684671134</v>
       </c>
       <c r="D23">
         <v>2.658306070519811</v>
       </c>
       <c r="E23">
-        <v>22.66529351184346</v>
+        <v>17.08341915550979</v>
       </c>
       <c r="F23">
         <v>60.25128733264676</v>
       </c>
       <c r="G23">
-        <v>17.08341915550979</v>
+        <v>22.66529351184346</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.49653442259138</v>
+      </c>
+      <c r="C24">
         <v>34.39846903494524</v>
-      </c>
-      <c r="C24">
-        <v>28.49653442259138</v>
       </c>
       <c r="D24">
         <v>2.907106124357176</v>
       </c>
       <c r="E24">
-        <v>21.11695773646747</v>
+        <v>17.49380510005627</v>
       </c>
       <c r="F24">
         <v>61.38923716347625</v>
       </c>
       <c r="G24">
-        <v>17.49380510005627</v>
+        <v>21.11695773646747</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.90619120150524</v>
+      </c>
+      <c r="C25">
         <v>51.84123286443867</v>
-      </c>
-      <c r="C25">
-        <v>26.90619120150524</v>
       </c>
       <c r="D25">
         <v>1.928966470791566</v>
       </c>
       <c r="E25">
-        <v>29.00250626566416</v>
+        <v>15.05263157894737</v>
       </c>
       <c r="F25">
         <v>55.94486215538847</v>
       </c>
       <c r="G25">
-        <v>15.05263157894737</v>
+        <v>29.00250626566416</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>31.77257525083612</v>
+      </c>
+      <c r="C26">
         <v>43.8834576794443</v>
-      </c>
-      <c r="C26">
-        <v>31.77257525083612</v>
       </c>
       <c r="D26">
         <v>2.278763007474718</v>
       </c>
       <c r="E26">
-        <v>24.98260774047087</v>
+        <v>18.08794991029256</v>
       </c>
       <c r="F26">
         <v>56.92944234923657</v>
       </c>
       <c r="G26">
-        <v>18.08794991029256</v>
+        <v>24.98260774047087</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.3279633712057</v>
+      </c>
+      <c r="C27">
         <v>51.54315753773105</v>
-      </c>
-      <c r="C27">
-        <v>28.3279633712057</v>
       </c>
       <c r="D27">
         <v>1.940121730547787</v>
       </c>
       <c r="E27">
-        <v>28.65560478929009</v>
+        <v>15.74903365701895</v>
       </c>
       <c r="F27">
         <v>55.59536155369096</v>
       </c>
       <c r="G27">
-        <v>15.74903365701895</v>
+        <v>28.65560478929009</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.183635690485</v>
+      </c>
+      <c r="C28">
         <v>55.59052202887819</v>
-      </c>
-      <c r="C28">
-        <v>29.183635690485</v>
       </c>
       <c r="D28">
         <v>1.798867798867799</v>
       </c>
       <c r="E28">
-        <v>30.08565846816611</v>
+        <v>15.79421930571558</v>
       </c>
       <c r="F28">
         <v>54.12012222611832</v>
       </c>
       <c r="G28">
-        <v>15.79421930571558</v>
+        <v>30.08565846816611</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>25.43984264014862</v>
+      </c>
+      <c r="C29">
         <v>34.94700032783302</v>
-      </c>
-      <c r="C29">
-        <v>25.43984264014862</v>
       </c>
       <c r="D29">
         <v>2.861475922451532</v>
       </c>
       <c r="E29">
-        <v>21.78919397697077</v>
+        <v>15.86155208830142</v>
       </c>
       <c r="F29">
         <v>62.34925393472781</v>
       </c>
       <c r="G29">
-        <v>15.86155208830142</v>
+        <v>21.78919397697077</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>29.07972177635099</v>
+      </c>
+      <c r="C30">
         <v>30.84155010318734</v>
-      </c>
-      <c r="C30">
-        <v>29.07972177635099</v>
       </c>
       <c r="D30">
         <v>3.242379182156134</v>
       </c>
       <c r="E30">
-        <v>19.2854582387382</v>
+        <v>18.18377344963556</v>
       </c>
       <c r="F30">
         <v>62.53076831162624</v>
       </c>
       <c r="G30">
-        <v>18.18377344963556</v>
+        <v>19.2854582387382</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.21721099015034</v>
+      </c>
+      <c r="C31">
         <v>34.35977190254017</v>
-      </c>
-      <c r="C31">
-        <v>29.21721099015034</v>
       </c>
       <c r="D31">
         <v>2.910380205190103</v>
       </c>
       <c r="E31">
+        <v>17.86144387399379</v>
+      </c>
+      <c r="F31">
+        <v>61.13329530328959</v>
+      </c>
+      <c r="G31">
         <v>21.00526082271661</v>
-      </c>
-      <c r="F31">
-        <v>61.13329530328961</v>
-      </c>
-      <c r="G31">
-        <v>17.86144387399379</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>33.89546571364753</v>
+      </c>
+      <c r="C32">
         <v>20.87335269153451</v>
-      </c>
-      <c r="C32">
-        <v>33.89546571364753</v>
       </c>
       <c r="D32">
         <v>4.79079721776351</v>
       </c>
       <c r="E32">
-        <v>13.48679463125992</v>
+        <v>21.9007071727522</v>
       </c>
       <c r="F32">
         <v>64.61249819598788</v>
       </c>
       <c r="G32">
-        <v>21.9007071727522</v>
+        <v>13.48679463125992</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>22.26586102719033</v>
+      </c>
+      <c r="C33">
         <v>25.98187311178248</v>
-      </c>
-      <c r="C33">
-        <v>22.26586102719033</v>
       </c>
       <c r="D33">
         <v>3.848837209302326</v>
       </c>
       <c r="E33">
-        <v>17.52598328917873</v>
+        <v>15.01936009781944</v>
       </c>
       <c r="F33">
         <v>67.45465661300183</v>
       </c>
       <c r="G33">
-        <v>15.01936009781944</v>
+        <v>17.52598328917873</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>29.8921832884097</v>
+      </c>
+      <c r="C34">
         <v>38.59838274932615</v>
-      </c>
-      <c r="C34">
-        <v>29.8921832884097</v>
       </c>
       <c r="D34">
         <v>2.590782122905028</v>
       </c>
       <c r="E34">
-        <v>22.90833466645336</v>
+        <v>17.74116141417374</v>
       </c>
       <c r="F34">
-        <v>59.35050391937289</v>
+        <v>59.3505039193729</v>
       </c>
       <c r="G34">
-        <v>17.74116141417373</v>
+        <v>22.90833466645337</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>29.74515800203874</v>
+      </c>
+      <c r="C35">
         <v>34.40366972477064</v>
-      </c>
-      <c r="C35">
-        <v>29.74515800203874</v>
       </c>
       <c r="D35">
         <v>2.906666666666667</v>
       </c>
       <c r="E35">
+        <v>18.12084704713407</v>
+      </c>
+      <c r="F35">
+        <v>60.92032540520399</v>
+      </c>
+      <c r="G35">
         <v>20.95882754766193</v>
-      </c>
-      <c r="F35">
-        <v>60.920325405204</v>
-      </c>
-      <c r="G35">
-        <v>18.12084704713407</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>25.38036622195038</v>
+      </c>
+      <c r="C36">
         <v>38.35773538743836</v>
-      </c>
-      <c r="C36">
-        <v>25.38036622195038</v>
       </c>
       <c r="D36">
         <v>2.607036077337054</v>
       </c>
       <c r="E36">
+        <v>15.50058659071144</v>
+      </c>
+      <c r="F36">
+        <v>61.07313998213963</v>
+      </c>
+      <c r="G36">
         <v>23.42627342714894</v>
-      </c>
-      <c r="F36">
-        <v>61.07313998213962</v>
-      </c>
-      <c r="G36">
-        <v>15.50058659071144</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>29.23099587507366</v>
+      </c>
+      <c r="C37">
         <v>34.79670005892752</v>
-      </c>
-      <c r="C37">
-        <v>29.23099587507366</v>
       </c>
       <c r="D37">
         <v>2.873835732430144</v>
       </c>
       <c r="E37">
-        <v>21.21391747947765</v>
+        <v>17.82076844317508</v>
       </c>
       <c r="F37">
         <v>60.96531407734727</v>
       </c>
       <c r="G37">
-        <v>17.82076844317508</v>
+        <v>21.21391747947765</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>28.90618665369334</v>
+      </c>
+      <c r="C38">
         <v>41.77410200275683</v>
-      </c>
-      <c r="C38">
-        <v>28.90618665369334</v>
       </c>
       <c r="D38">
         <v>2.393827639751553</v>
       </c>
       <c r="E38">
-        <v>24.47505938242281</v>
+        <v>16.93586698337293</v>
       </c>
       <c r="F38">
         <v>58.58907363420428</v>
       </c>
       <c r="G38">
-        <v>16.93586698337293</v>
+        <v>24.47505938242281</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>28.79660687375431</v>
+      </c>
+      <c r="C39">
         <v>35.73841816148948</v>
-      </c>
-      <c r="C39">
-        <v>28.79660687375431</v>
       </c>
       <c r="D39">
         <v>2.79810929370558</v>
       </c>
       <c r="E39">
-        <v>21.72085740032204</v>
+        <v>17.50180964058322</v>
       </c>
       <c r="F39">
         <v>60.77733295909474</v>
       </c>
       <c r="G39">
-        <v>17.50180964058322</v>
+        <v>21.72085740032204</v>
       </c>
     </row>
   </sheetData>
